--- a/data/output/2025/evaluasi_94.xlsx
+++ b/data/output/2025/evaluasi_94.xlsx
@@ -1208,7 +1208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1352,6 +1352,174 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9427</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Supiori</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>23.78653198160535</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9427</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Supiori</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-19.30942292142579</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9427</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Supiori</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5.164756172787127</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9427</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Supiori</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-8.666632429928615</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9427</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Supiori</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.3722752797739521</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9427</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Supiori</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.7945666738779056</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1636,18 +1804,242 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>11.17933793892213</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9428</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamberamo Raya</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>14.00324210983054</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9428</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamberamo Raya</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>28.61727069157996</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9428</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamberamo Raya</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-28.7881503062157</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9428</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamberamo Raya</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>27.29970184860017</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9428</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamberamo Raya</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>33.89713418155163</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9428</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamberamo Raya</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-10.48956972593453</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9428</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamberamo Raya</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>25.48371731583643</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9428</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamberamo Raya</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>3.319186730199317</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_q4-25</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -1664,7 +2056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1920,6 +2312,202 @@
       <c r="F9" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9403</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Jayapura</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>8.691829194626113</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9403</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Jayapura</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>26.9924617218417</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9403</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Jayapura</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-18.51208934139686</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9403</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Jayapura</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4.708078051695246</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9403</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Jayapura</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-10.66454285767584</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9403</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Jayapura</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.5546087894575642</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9403</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Jayapura</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.6627696412638725</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1934,7 +2522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2218,6 +2806,174 @@
       <c r="F10" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9420</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Keerom</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>24.33239072333944</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9420</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Keerom</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-20.31124932945349</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9420</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Keerom</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5.404815160625787</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9420</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Keerom</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-9.845097031059895</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9420</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Keerom</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>6.869568951633534</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q4-25_prov vs implisit_y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9420</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Keerom</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>5.998120189127854</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_2025_prov vs implisit_y-on-y_pkrt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2516,6 +3272,230 @@
       <c r="F10" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9409</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Biak Numfor</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>22.01770917885745</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9409</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Biak Numfor</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-20.40358473409126</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9409</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Biak Numfor</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3.767769260475698</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9409</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Biak Numfor</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-10.1973300606209</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9409</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Biak Numfor</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.05229843324046988</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9409</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Biak Numfor</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.6354774548012687</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9409</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Biak Numfor</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-1.01131034885822</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9409</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Biak Numfor</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>5.006773417576455</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q4-25_prov vs implisit_y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2530,7 +3510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2786,6 +3766,146 @@
       <c r="F9" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9426</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Waropen</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>23.43622568695758</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9426</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Waropen</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-12.45375870686378</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9426</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Waropen</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5.309819582789097</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9426</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Waropen</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-6.487217813622083</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9426</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Waropen</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5.99498023956887</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q4-25_prov vs implisit_y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2800,7 +3920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3210,18 +4330,186 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D15" t="n">
+        <v>33.61733336976769</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9471</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kota Jayapura</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-25.04822237658136</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9471</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kota Jayapura</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-8.494824315721758</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9471</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kota Jayapura</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-4.351248969454737</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>9471</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kota Jayapura</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.5824704523556119</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>9471</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kota Jayapura</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.1523289437103547</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>9471</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kota Jayapura</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>-2.782398529234133</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>sog_q_pi_q4-25</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -3238,7 +4526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3494,6 +4782,118 @@
       <c r="F9" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9408</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Yapen</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>25.66895763996014</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9408</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Yapen</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-16.04849167489103</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9408</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Yapen</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5.222705260577701</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9408</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Yapen</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-7.17489187707471</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3508,7 +4908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3711,6 +5111,202 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9419</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Sarmi</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>27.7327405233583</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9419</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Sarmi</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12.40529067938803</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9419</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Sarmi</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-15.07544166401898</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9419</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Sarmi</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4.109546047318638</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9419</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Sarmi</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-7.81339385285747</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9419</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Sarmi</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>7.471635648745154</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q4-25_prov vs implisit_y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9419</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Sarmi</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5.899587036398241</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_2025_prov vs implisit_y-on-y_pkrt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
